--- a/파이썬/코딩교실/1.코딩교실준비/5.LMS줌링크/LMS줌링크.xlsx
+++ b/파이썬/코딩교실/1.코딩교실준비/5.LMS줌링크/LMS줌링크.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\5.LMS줌링크\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실\1.코딩교실준비\5.LMS줌링크\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C466CBB-74E3-497D-B1FF-28E8DDAB6079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A3C93B-01BF-47A0-8D65-5D91657725B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34455" yWindow="2505" windowWidth="28860" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>admin ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,172 +107,145 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BG_MW_01</t>
-  </si>
-  <si>
-    <t>BG_MW_02</t>
-  </si>
-  <si>
-    <t>BG_MW_03</t>
-  </si>
-  <si>
-    <t>BG_MW_04</t>
-  </si>
-  <si>
-    <t>BG_MW_05</t>
-  </si>
-  <si>
-    <t>BG_MW_06</t>
-  </si>
-  <si>
-    <t>BG_MW_07</t>
-  </si>
-  <si>
-    <t>BG_MW_08</t>
-  </si>
-  <si>
-    <t>BG_MW_09</t>
-  </si>
-  <si>
-    <t>BG_MW_10</t>
-  </si>
-  <si>
-    <t>BG_MW_11</t>
-  </si>
-  <si>
-    <t>BG_MW_12</t>
-  </si>
-  <si>
-    <t>BG_MW_13</t>
-  </si>
-  <si>
-    <t>BG_MW_14</t>
-  </si>
-  <si>
-    <t>BG_MW_15</t>
-  </si>
-  <si>
-    <t>BG_MW_16</t>
-  </si>
-  <si>
-    <t>BG_MW_17</t>
-  </si>
-  <si>
-    <t>BG_MW_18</t>
-  </si>
-  <si>
-    <t>BG_TT_01</t>
-  </si>
-  <si>
-    <t>BG_TT_02</t>
-  </si>
-  <si>
-    <t>BG_TT_03</t>
-  </si>
-  <si>
-    <t>BG_TT_04</t>
-  </si>
-  <si>
-    <t>BG_TT_05</t>
-  </si>
-  <si>
-    <t>BG_TT_06</t>
-  </si>
-  <si>
-    <t>BG_TT_07</t>
-  </si>
-  <si>
-    <t>BG_TT_08</t>
-  </si>
-  <si>
-    <t>BG_TT_09</t>
-  </si>
-  <si>
-    <t>BG_TT_10</t>
-  </si>
-  <si>
-    <t>BG_TT_11</t>
-  </si>
-  <si>
-    <t>BG_TT_12</t>
-  </si>
-  <si>
-    <t>BG_TT_13</t>
-  </si>
-  <si>
-    <t>BG_TT_14</t>
-  </si>
-  <si>
-    <t>BG_TT_15</t>
-  </si>
-  <si>
-    <t>BG_TT_16</t>
-  </si>
-  <si>
-    <t>BG_TT_17</t>
-  </si>
-  <si>
-    <t>BG_TT_18</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/89267054774?pwd=pB6yYaiybb1GsxJLjgzgJcBjuBaBgr.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/87481279863?pwd=wAxjnajBbbdykfhrhUYRf78kAbaxYI.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/89828821645?pwd=Jbu7yJCuXqXbtJnWZrEq3hPtaCEOu4.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84946198891?pwd=YS0puaT5SS0sLbuLbaIuPRTC3PVlh9.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/88629906192?pwd=ClfMqFS1dZ4rCI3hze6QNI6VnoVjkc.1</t>
-  </si>
-  <si>
-    <t>BG_TT_19</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/88260643671?pwd=etPerEnQW3KEUlcE2Q7YQQpk3WMmTA.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81193221983?pwd=dlaX4n2zJJbrzv88yv0Q9w7ezeIlxv.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/85718103327?pwd=NmEhhhRk2aEnQHtwNzYNFglQaET8uQ.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86217792106?pwd=Knxr51BVj1c7s3bHUhYo2V4vSnKOfI.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/89271860506?pwd=LOyyEtbCJjxFmGd5baRGb3DuY9kIy4.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81959809961?pwd=QyUjNfW0n3bjrFaw6U3BBua0b07Gxr.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83983224518?pwd=0H5HHnogqWjHQyaZhrTQWwprObX8Z9.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84969155425?pwd=X0vlZ5TJOQSwVyVb6GMSHy0xQAiKkv.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/84386193333?pwd=bO3IYLi0jtoUIYLkIduxNtFnn6v0Jt.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86959584428?pwd=kMvA0at3ciRC3UEF8tOSbQEGwhiwo2.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86336628154?pwd=KVC2uLz1S7OfLqYXJXJpX3CUwmcLhJ.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/85808556380?pwd=WeJ25UbtJxbDi6WTSQhVBKfcBbSp2E.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82150657982?pwd=y5poP1hNSQaChg52ee57x1ITzPP4ux.1</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82381821972?pwd=1wo9aFRAfODSTxoQmQr67VCIinxf8P.1</t>
+    <t>PH_MW_01</t>
+  </si>
+  <si>
+    <t>PH_MW_02</t>
+  </si>
+  <si>
+    <t>PH_MW_03</t>
+  </si>
+  <si>
+    <t>PH_MW_04</t>
+  </si>
+  <si>
+    <t>PH_MW_05</t>
+  </si>
+  <si>
+    <t>PH_MW_06</t>
+  </si>
+  <si>
+    <t>PH_MW_07</t>
+  </si>
+  <si>
+    <t>PH_MW_08</t>
+  </si>
+  <si>
+    <t>PH_MW_09</t>
+  </si>
+  <si>
+    <t>PH_MW_10</t>
+  </si>
+  <si>
+    <t>PH_MW_11</t>
+  </si>
+  <si>
+    <t>PH_MW_12</t>
+  </si>
+  <si>
+    <t>PH_MW_13</t>
+  </si>
+  <si>
+    <t>PH_MW_14</t>
+  </si>
+  <si>
+    <t>PH_MW_15</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/82548184021?pwd=41MviR3M9dZNBWpbVafapUYfVlmYMX.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/89618170410?pwd=yLtmXLPkhYEyyBScxu1V5O0aIXfBDu.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/86579231577?pwd=sdu6zSrvYRRnCU9SGBAkl1129IvEHx.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/88986494464?pwd=6cQNaqO21xnd5OMbIrk2gcZOedUDr6.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/87142441764?pwd=bIDYopu3hstp9blKYTN0u5CBUNBlfn.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/81870478825?pwd=YzA8oJpcjb2pzpSP2OIMPq7s47wL9b.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/89477012786?pwd=SZbkBo8ncpOW3leTXKkGOj7dYfphm2.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/83136293898?pwd=VDOPSaozM1RhWaGC0zSdI4V4XJ6erp.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/81272582830?pwd=ru8aBJrxAcqrzIHHNW8PWcxAlaWuk5.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/82540019511?pwd=CR2dJ3YorSvLKkeIGboAMeJZSaHWGM.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/84967311073?pwd=srIGeEzKZwf5LsbcvDVqMud5X32uZD.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/87995591846?pwd=t3aW2tpQaL1rqnALg20KQvRRG5Dw8C.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/86351484527?pwd=S0PFfkgd9Ki4pq0nAYGRj6DRUjAOhy.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/86573040681?pwd=Ecvl8J4UTgCUlbAKPlmxJBqAXGRbBB.1</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/85157592885?pwd=lCjuboXDjroTuiYfguOrAfSSPVB3SH.1</t>
+  </si>
+  <si>
+    <t>PH_TT_01</t>
+  </si>
+  <si>
+    <t>PH_TT_02</t>
+  </si>
+  <si>
+    <t>PH_TT_03</t>
+  </si>
+  <si>
+    <t>PH_TT_04</t>
+  </si>
+  <si>
+    <t>PH_TT_05</t>
+  </si>
+  <si>
+    <t>PH_TT_06</t>
+  </si>
+  <si>
+    <t>PH_TT_07</t>
+  </si>
+  <si>
+    <t>PH_TT_08</t>
+  </si>
+  <si>
+    <t>PH_TT_09</t>
+  </si>
+  <si>
+    <t>PH_TT_10</t>
+  </si>
+  <si>
+    <t>PH_TT_11</t>
+  </si>
+  <si>
+    <t>PH_TT_12</t>
+  </si>
+  <si>
+    <t>PH_TT_13</t>
+  </si>
+  <si>
+    <t>PH_TT_14</t>
+  </si>
+  <si>
+    <t>PH_TT_15</t>
+  </si>
+  <si>
+    <t>PH_TT_16</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/j/81542056522?pwd=ASF30rjm4UnYRAVBIbDNwHaY7KAnGr.1</t>
   </si>
 </sst>
 </file>
@@ -534,9 +508,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -574,7 +548,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -680,7 +654,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -822,7 +796,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -831,28 +805,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q52"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="93" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="2" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="10.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="2" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="20.5" style="5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.09765625" style="2" hidden="1" customWidth="1"/>
     <col min="9" max="10" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13.3984375" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" style="2" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="7.09765625" style="2" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="2"/>
-    <col min="16" max="16" width="18.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="18.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="44.8984375" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17.25" thickBot="1">
+    <row r="1" spans="1:17" ht="18" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -864,15 +838,15 @@
         <v>2</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="18" thickTop="1" thickBot="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A2" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C2" s="8"/>
       <c r="F2" s="4"/>
@@ -882,15 +856,15 @@
         <v>7</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="17.25" thickBot="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="18" thickBot="1">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6"/>
       <c r="F3" s="4"/>
@@ -903,12 +877,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="17.25" thickBot="1">
+    <row r="4" spans="1:17" ht="18" thickBot="1">
       <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="4"/>
@@ -921,36 +895,36 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17.25" thickBot="1">
+    <row r="5" spans="1:17" ht="18" thickBot="1">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="17.25" thickBot="1">
+    <row r="6" spans="1:17" ht="18" thickBot="1">
       <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C6" s="6"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="17.25" thickBot="1">
+    <row r="7" spans="1:17" ht="18" thickBot="1">
       <c r="A7" s="11" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C7" s="6"/>
       <c r="F7" s="4"/>
@@ -963,12 +937,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="17.25" thickBot="1">
+    <row r="8" spans="1:17" ht="18" thickBot="1">
       <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C8" s="6"/>
       <c r="F8" s="4"/>
@@ -978,12 +952,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.25" thickBot="1">
+    <row r="9" spans="1:17" ht="18" thickBot="1">
       <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C9" s="7"/>
       <c r="F9" s="4"/>
@@ -996,12 +970,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="17.25" thickBot="1">
+    <row r="10" spans="1:17" ht="18" thickBot="1">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6"/>
       <c r="F10" s="4"/>
@@ -1011,12 +985,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="17.25" thickBot="1">
+    <row r="11" spans="1:17" ht="18" thickBot="1">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C11" s="6"/>
       <c r="F11" s="4"/>
@@ -1029,12 +1003,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.25" thickBot="1">
+    <row r="12" spans="1:17" ht="18" thickBot="1">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="C12" s="6"/>
       <c r="F12" s="4"/>
@@ -1044,319 +1018,295 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.25" thickBot="1">
+    <row r="13" spans="1:17" ht="18" thickBot="1">
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C13" s="6"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:17" ht="17.25" thickBot="1">
+    <row r="14" spans="1:17" ht="18" thickBot="1">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C14" s="6"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:17" ht="17.25" thickBot="1">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:17" ht="18" thickBot="1">
+      <c r="A15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>70</v>
+      <c r="B15" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="6"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:17" ht="17.25" thickBot="1">
+    <row r="16" spans="1:17" ht="18" thickBot="1">
       <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>55</v>
+      <c r="B16" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C16" s="6"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:11" ht="18" thickTop="1" thickBot="1">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:11" ht="18.600000000000001" thickTop="1" thickBot="1">
+      <c r="A17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>56</v>
       </c>
       <c r="C17" s="8"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="17.25" thickBot="1">
+    <row r="18" spans="1:11" ht="18" thickBot="1">
       <c r="A18" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>57</v>
       </c>
       <c r="C18" s="6"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:11" ht="18" thickBot="1">
+      <c r="A19" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="19" t="s">
         <v>34</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>71</v>
       </c>
       <c r="C19" s="6"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2"/>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:11" ht="18" thickBot="1">
+      <c r="A20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>35</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>59</v>
       </c>
       <c r="C20" s="6"/>
       <c r="F20" s="4"/>
       <c r="G20" s="2"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:11" ht="18" thickBot="1">
+      <c r="A21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>36</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>60</v>
       </c>
       <c r="C21" s="6"/>
       <c r="F21" s="4"/>
       <c r="G21" s="2"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A22" s="12" t="s">
+    <row r="22" spans="1:11" ht="18" thickBot="1">
+      <c r="A22" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>37</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>61</v>
       </c>
       <c r="C22" s="13"/>
       <c r="F22" s="4"/>
       <c r="G22" s="2"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:11" ht="18" thickBot="1">
+      <c r="A23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="19" t="s">
         <v>38</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="C23" s="7"/>
       <c r="F23" s="4"/>
       <c r="G23" s="2"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:11" ht="18" thickBot="1">
+      <c r="A24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>63</v>
       </c>
       <c r="C24" s="6"/>
       <c r="F24" s="4"/>
       <c r="G24" s="2"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:11" ht="18" thickBot="1">
+      <c r="A25" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>54</v>
       </c>
       <c r="C25" s="6"/>
       <c r="F25" s="4"/>
       <c r="G25" s="2"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A26" s="12" t="s">
+    <row r="26" spans="1:11" ht="18" thickBot="1">
+      <c r="A26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>64</v>
       </c>
       <c r="C26" s="6"/>
       <c r="F26" s="4"/>
       <c r="G26" s="2"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:11" ht="18" thickBot="1">
+      <c r="A27" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="19" t="s">
         <v>42</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>65</v>
       </c>
       <c r="C27" s="6"/>
       <c r="F27" s="4"/>
       <c r="G27" s="2"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:11" ht="18" thickTop="1" thickBot="1">
-      <c r="A28" s="12" t="s">
+    <row r="28" spans="1:11" ht="18.600000000000001" thickTop="1" thickBot="1">
+      <c r="A28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>66</v>
       </c>
       <c r="C28" s="8"/>
       <c r="F28" s="4"/>
       <c r="G28" s="2"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:11" ht="18" thickBot="1">
+      <c r="A29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>67</v>
       </c>
       <c r="C29" s="6"/>
       <c r="F29" s="4"/>
       <c r="G29" s="2"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A30" s="12" t="s">
+    <row r="30" spans="1:11" ht="18" thickBot="1">
+      <c r="A30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>68</v>
       </c>
       <c r="C30" s="6"/>
       <c r="F30" s="4"/>
       <c r="G30" s="2"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A31" s="11" t="s">
+    <row r="31" spans="1:11" ht="18" thickBot="1">
+      <c r="A31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>69</v>
       </c>
       <c r="C31" s="6"/>
       <c r="F31" s="4"/>
       <c r="G31" s="2"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A32" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>53</v>
+    <row r="32" spans="1:11" ht="18" thickBot="1">
+      <c r="A32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C32" s="6"/>
       <c r="F32" s="4"/>
       <c r="G32" s="2"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A33" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>70</v>
-      </c>
+    <row r="33" spans="1:11" ht="18" thickBot="1">
+      <c r="A33" s="11"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="6"/>
       <c r="F33" s="4"/>
       <c r="G33" s="2"/>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A34" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>55</v>
-      </c>
+    <row r="34" spans="1:11" ht="18" thickBot="1">
+      <c r="A34" s="12"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="6"/>
       <c r="F34" s="4"/>
       <c r="G34" s="2"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A35" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>56</v>
-      </c>
+    <row r="35" spans="1:11" ht="18" thickBot="1">
+      <c r="A35" s="11"/>
+      <c r="B35" s="18"/>
       <c r="C35" s="7"/>
       <c r="F35" s="4"/>
       <c r="G35" s="2"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A36" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>57</v>
-      </c>
+    <row r="36" spans="1:11" ht="18" thickBot="1">
+      <c r="A36" s="12"/>
+      <c r="B36" s="19"/>
       <c r="C36" s="6"/>
       <c r="F36" s="4"/>
       <c r="G36" s="2"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A37" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>71</v>
-      </c>
+    <row r="37" spans="1:11" ht="18" thickBot="1">
+      <c r="A37" s="11"/>
+      <c r="B37" s="20"/>
       <c r="C37" s="6"/>
       <c r="F37" s="4"/>
       <c r="G37" s="2"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11" ht="17.25" thickBot="1">
-      <c r="A38" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>72</v>
-      </c>
+    <row r="38" spans="1:11" ht="18" thickBot="1">
+      <c r="A38" s="12"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="6"/>
       <c r="F38" s="4"/>
       <c r="G38" s="2"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:11" ht="17.25" thickBot="1">
+    <row r="39" spans="1:11" ht="18" thickBot="1">
       <c r="A39" s="12"/>
       <c r="B39" s="16"/>
       <c r="C39" s="6"/>
@@ -1364,7 +1314,7 @@
       <c r="G39" s="2"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" ht="17.25" thickBot="1">
+    <row r="40" spans="1:11" ht="18" thickBot="1">
       <c r="A40" s="11"/>
       <c r="B40" s="16"/>
       <c r="C40" s="6"/>
@@ -1372,7 +1322,7 @@
       <c r="G40" s="2"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11" ht="17.25" thickBot="1">
+    <row r="41" spans="1:11" ht="18" thickBot="1">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
       <c r="C41" s="6"/>
@@ -1380,7 +1330,7 @@
       <c r="G41" s="2"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="18" thickTop="1" thickBot="1">
+    <row r="42" spans="1:11" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
       <c r="C42" s="8"/>
@@ -1388,7 +1338,7 @@
       <c r="G42" s="2"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11" ht="17.25" thickBot="1">
+    <row r="43" spans="1:11" ht="18" thickBot="1">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
       <c r="C43" s="6"/>
@@ -1396,7 +1346,7 @@
       <c r="G43" s="2"/>
       <c r="K43" s="4"/>
     </row>
-    <row r="44" spans="1:11" ht="17.25" thickBot="1">
+    <row r="44" spans="1:11" ht="18" thickBot="1">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
       <c r="C44" s="6"/>
@@ -1404,7 +1354,7 @@
       <c r="G44" s="2"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11" ht="17.25" thickBot="1">
+    <row r="45" spans="1:11" ht="18" thickBot="1">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
       <c r="C45" s="6"/>
@@ -1412,7 +1362,7 @@
       <c r="G45" s="2"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11" ht="17.25" thickBot="1">
+    <row r="46" spans="1:11" ht="18" thickBot="1">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
       <c r="C46" s="6"/>
@@ -1420,39 +1370,37 @@
       <c r="G46" s="2"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:11" ht="17.25" thickBot="1">
+    <row r="47" spans="1:11" ht="18" thickBot="1">
       <c r="C47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="17.25" thickBot="1">
+    <row r="48" spans="1:11" ht="18" thickBot="1">
       <c r="C48" s="6"/>
     </row>
-    <row r="49" spans="3:3" ht="17.25" thickBot="1">
+    <row r="49" spans="3:3" ht="18" thickBot="1">
       <c r="C49" s="7"/>
     </row>
-    <row r="50" spans="3:3" ht="18" thickTop="1" thickBot="1">
+    <row r="50" spans="3:3" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="C50" s="6"/>
     </row>
-    <row r="51" spans="3:3" ht="17.25" thickBot="1">
+    <row r="51" spans="3:3" ht="18" thickBot="1">
       <c r="C51" s="6"/>
     </row>
-    <row r="52" spans="3:3" ht="17.25" thickBot="1">
+    <row r="52" spans="3:3" ht="18" thickBot="1">
       <c r="C52" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="Q1" r:id="rId1" xr:uid="{FE21F267-E533-4861-88D0-C07536AB6D58}"/>
-    <hyperlink ref="Q2" r:id="rId2" xr:uid="{9FFE7ACE-1824-4C57-9BE1-CD3455AEF567}"/>
-    <hyperlink ref="Q7" r:id="rId3" xr:uid="{2F15D1DC-4C2D-4B8F-9E46-EA9A5702A39B}"/>
-    <hyperlink ref="Q9" r:id="rId4" xr:uid="{B810DE77-7A3B-465F-B768-9300AA75E360}"/>
-    <hyperlink ref="Q10" r:id="rId5" xr:uid="{045248DF-4C4F-47FD-80F3-BD1D5FEF4441}"/>
-    <hyperlink ref="Q8" r:id="rId6" xr:uid="{3477DE43-A923-49D1-9667-8086CCC36BC6}"/>
-    <hyperlink ref="Q12" r:id="rId7" xr:uid="{89C02FA0-7825-47D3-A436-BFC9A9FA2DBA}"/>
-    <hyperlink ref="Q11" r:id="rId8" xr:uid="{F2A7AEFA-0A9D-4E62-9B56-23C5471E41EA}"/>
-    <hyperlink ref="B19" r:id="rId9" xr:uid="{DBFB8D0D-D925-4F2B-AC89-613C41E1ABC7}"/>
-    <hyperlink ref="B37" r:id="rId10" xr:uid="{F675ACE0-774F-468D-AAD9-5FC75B110487}"/>
+    <hyperlink ref="Q7" r:id="rId1" xr:uid="{2F15D1DC-4C2D-4B8F-9E46-EA9A5702A39B}"/>
+    <hyperlink ref="Q9" r:id="rId2" xr:uid="{B810DE77-7A3B-465F-B768-9300AA75E360}"/>
+    <hyperlink ref="Q10" r:id="rId3" xr:uid="{045248DF-4C4F-47FD-80F3-BD1D5FEF4441}"/>
+    <hyperlink ref="Q8" r:id="rId4" xr:uid="{3477DE43-A923-49D1-9667-8086CCC36BC6}"/>
+    <hyperlink ref="Q12" r:id="rId5" xr:uid="{89C02FA0-7825-47D3-A436-BFC9A9FA2DBA}"/>
+    <hyperlink ref="Q11" r:id="rId6" xr:uid="{F2A7AEFA-0A9D-4E62-9B56-23C5471E41EA}"/>
+    <hyperlink ref="Q1" r:id="rId7" xr:uid="{602B4E38-D1BA-448F-9D51-279F9E5D4B0A}"/>
+    <hyperlink ref="Q2" r:id="rId8" xr:uid="{F46113D0-71BE-4D9C-B973-7B21A3074FD7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>